--- a/Team-Data/2007-08/3-26-2007-08.xlsx
+++ b/Team-Data/2007-08/3-26-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,61 +728,61 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E2" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F2" t="n">
         <v>40</v>
       </c>
       <c r="G2" t="n">
-        <v>0.437</v>
+        <v>0.429</v>
       </c>
       <c r="H2" t="n">
         <v>48.4</v>
       </c>
       <c r="I2" t="n">
-        <v>35.8</v>
+        <v>35.7</v>
       </c>
       <c r="J2" t="n">
-        <v>79.59999999999999</v>
+        <v>79.7</v>
       </c>
       <c r="K2" t="n">
-        <v>0.45</v>
+        <v>0.448</v>
       </c>
       <c r="L2" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="M2" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="N2" t="n">
-        <v>0.353</v>
+        <v>0.352</v>
       </c>
       <c r="O2" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="P2" t="n">
         <v>27.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.773</v>
+        <v>0.774</v>
       </c>
       <c r="R2" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S2" t="n">
-        <v>29.9</v>
+        <v>30.1</v>
       </c>
       <c r="T2" t="n">
-        <v>42.2</v>
+        <v>42.4</v>
       </c>
       <c r="U2" t="n">
-        <v>21.6</v>
+        <v>21.5</v>
       </c>
       <c r="V2" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W2" t="n">
         <v>7.4</v>
@@ -730,16 +797,16 @@
         <v>20.7</v>
       </c>
       <c r="AA2" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="AB2" t="n">
-        <v>97</v>
+        <v>96.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>-2</v>
+        <v>-2.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE2" t="n">
         <v>19</v>
@@ -751,7 +818,7 @@
         <v>19</v>
       </c>
       <c r="AH2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI2" t="n">
         <v>24</v>
@@ -760,7 +827,7 @@
         <v>22</v>
       </c>
       <c r="AK2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL2" t="n">
         <v>27</v>
@@ -781,19 +848,19 @@
         <v>7</v>
       </c>
       <c r="AR2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AS2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU2" t="n">
         <v>14</v>
       </c>
       <c r="AV2" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AW2" t="n">
         <v>14</v>
@@ -805,16 +872,16 @@
         <v>24</v>
       </c>
       <c r="AZ2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA2" t="n">
         <v>10</v>
       </c>
       <c r="BB2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -843,34 +910,34 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E3" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="F3" t="n">
         <v>15</v>
       </c>
       <c r="G3" t="n">
-        <v>0.789</v>
+        <v>0.786</v>
       </c>
       <c r="H3" t="n">
         <v>48.1</v>
       </c>
       <c r="I3" t="n">
-        <v>36.4</v>
+        <v>36.3</v>
       </c>
       <c r="J3" t="n">
-        <v>76.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.476</v>
+        <v>0.475</v>
       </c>
       <c r="L3" t="n">
         <v>7.2</v>
       </c>
       <c r="M3" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="N3" t="n">
         <v>0.38</v>
@@ -885,10 +952,10 @@
         <v>0.77</v>
       </c>
       <c r="R3" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T3" t="n">
         <v>41.4</v>
@@ -909,19 +976,19 @@
         <v>4.9</v>
       </c>
       <c r="Z3" t="n">
-        <v>22.6</v>
+        <v>22.7</v>
       </c>
       <c r="AA3" t="n">
         <v>22.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.5</v>
+        <v>100.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="AD3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,7 +1003,7 @@
         <v>24</v>
       </c>
       <c r="AI3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -969,7 +1036,7 @@
         <v>9</v>
       </c>
       <c r="AT3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU3" t="n">
         <v>10</v>
@@ -984,7 +1051,7 @@
         <v>18</v>
       </c>
       <c r="AY3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ3" t="n">
         <v>25</v>
@@ -993,7 +1060,7 @@
         <v>6</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -1025,37 +1092,37 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" t="n">
         <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>0.366</v>
+        <v>0.357</v>
       </c>
       <c r="H4" t="n">
         <v>48.5</v>
       </c>
       <c r="I4" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J4" t="n">
         <v>79.8</v>
       </c>
       <c r="K4" t="n">
-        <v>0.447</v>
+        <v>0.446</v>
       </c>
       <c r="L4" t="n">
         <v>6.4</v>
       </c>
       <c r="M4" t="n">
-        <v>17.6</v>
+        <v>17.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0.365</v>
+        <v>0.363</v>
       </c>
       <c r="O4" t="n">
         <v>18.2</v>
@@ -1070,16 +1137,16 @@
         <v>11.1</v>
       </c>
       <c r="S4" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="T4" t="n">
-        <v>40.7</v>
+        <v>40.6</v>
       </c>
       <c r="U4" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="V4" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W4" t="n">
         <v>7.5</v>
@@ -1097,13 +1164,13 @@
         <v>21</v>
       </c>
       <c r="AB4" t="n">
-        <v>96</v>
+        <v>95.8</v>
       </c>
       <c r="AC4" t="n">
-        <v>-4.9</v>
+        <v>-5.2</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE4" t="n">
         <v>23</v>
@@ -1118,13 +1185,13 @@
         <v>3</v>
       </c>
       <c r="AI4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ4" t="n">
         <v>21</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AL4" t="n">
         <v>16</v>
@@ -1133,7 +1200,7 @@
         <v>15</v>
       </c>
       <c r="AN4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO4" t="n">
         <v>20</v>
@@ -1154,10 +1221,10 @@
         <v>25</v>
       </c>
       <c r="AU4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AV4" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AW4" t="n">
         <v>13</v>
@@ -1175,7 +1242,7 @@
         <v>16</v>
       </c>
       <c r="BB4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BC4" t="n">
         <v>23</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E5" t="n">
         <v>28</v>
       </c>
       <c r="F5" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G5" t="n">
-        <v>0.394</v>
+        <v>0.4</v>
       </c>
       <c r="H5" t="n">
         <v>48.4</v>
@@ -1231,22 +1298,22 @@
         <v>0.43</v>
       </c>
       <c r="L5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="M5" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="N5" t="n">
-        <v>0.36</v>
+        <v>0.358</v>
       </c>
       <c r="O5" t="n">
-        <v>18.6</v>
+        <v>18.5</v>
       </c>
       <c r="P5" t="n">
         <v>24.7</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.753</v>
+        <v>0.752</v>
       </c>
       <c r="R5" t="n">
         <v>13.4</v>
@@ -1264,7 +1331,7 @@
         <v>14.5</v>
       </c>
       <c r="W5" t="n">
-        <v>7.6</v>
+        <v>7.7</v>
       </c>
       <c r="X5" t="n">
         <v>5.1</v>
@@ -1279,13 +1346,13 @@
         <v>21.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>96.8</v>
+        <v>96.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>-2.8</v>
+        <v>-2.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE5" t="n">
         <v>22</v>
@@ -1297,10 +1364,10 @@
         <v>22</v>
       </c>
       <c r="AH5" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI5" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AJ5" t="n">
         <v>5</v>
@@ -1318,7 +1385,7 @@
         <v>16</v>
       </c>
       <c r="AO5" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AP5" t="n">
         <v>17</v>
@@ -1330,7 +1397,7 @@
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AT5" t="n">
         <v>6</v>
@@ -1339,10 +1406,10 @@
         <v>11</v>
       </c>
       <c r="AV5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AW5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX5" t="n">
         <v>7</v>
@@ -1357,7 +1424,7 @@
         <v>13</v>
       </c>
       <c r="BB5" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BC5" t="n">
         <v>21</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -1389,28 +1456,28 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E6" t="n">
         <v>40</v>
       </c>
       <c r="F6" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G6" t="n">
-        <v>0.556</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>48.5</v>
       </c>
       <c r="I6" t="n">
-        <v>36</v>
+        <v>35.9</v>
       </c>
       <c r="J6" t="n">
         <v>81.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.44</v>
+        <v>0.439</v>
       </c>
       <c r="L6" t="n">
         <v>7.1</v>
@@ -1419,28 +1486,28 @@
         <v>19.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.363</v>
+        <v>0.364</v>
       </c>
       <c r="O6" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="P6" t="n">
-        <v>25</v>
+        <v>25.1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.721</v>
+        <v>0.722</v>
       </c>
       <c r="R6" t="n">
-        <v>13.2</v>
+        <v>13.1</v>
       </c>
       <c r="S6" t="n">
-        <v>31.3</v>
+        <v>31.4</v>
       </c>
       <c r="T6" t="n">
         <v>44.5</v>
       </c>
       <c r="U6" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V6" t="n">
         <v>14.1</v>
@@ -1458,7 +1525,7 @@
         <v>21.2</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.1</v>
+        <v>20.2</v>
       </c>
       <c r="AB6" t="n">
         <v>97.09999999999999</v>
@@ -1467,7 +1534,7 @@
         <v>-0.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1479,13 +1546,13 @@
         <v>13</v>
       </c>
       <c r="AH6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI6" t="n">
         <v>22</v>
       </c>
       <c r="AJ6" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AK6" t="n">
         <v>27</v>
@@ -1497,40 +1564,40 @@
         <v>10</v>
       </c>
       <c r="AN6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AO6" t="n">
         <v>21</v>
       </c>
       <c r="AP6" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ6" t="n">
         <v>28</v>
       </c>
       <c r="AR6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AS6" t="n">
         <v>11</v>
       </c>
       <c r="AT6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AV6" t="n">
         <v>10</v>
       </c>
       <c r="AW6" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AY6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ6" t="n">
         <v>17</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>4.7</v>
       </c>
       <c r="AD7" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE7" t="n">
         <v>10</v>
@@ -1661,7 +1728,7 @@
         <v>9</v>
       </c>
       <c r="AH7" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AI7" t="n">
         <v>17</v>
@@ -1676,7 +1743,7 @@
         <v>19</v>
       </c>
       <c r="AM7" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AN7" t="n">
         <v>17</v>
@@ -1709,7 +1776,7 @@
         <v>29</v>
       </c>
       <c r="AX7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY7" t="n">
         <v>8</v>
@@ -1718,13 +1785,13 @@
         <v>22</v>
       </c>
       <c r="BA7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB7" t="n">
         <v>12</v>
       </c>
       <c r="BC7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="AE8" t="n">
         <v>11</v>
@@ -1843,7 +1910,7 @@
         <v>12</v>
       </c>
       <c r="AH8" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AI8" t="n">
         <v>4</v>
@@ -1858,7 +1925,7 @@
         <v>13</v>
       </c>
       <c r="AM8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN8" t="n">
         <v>15</v>
@@ -1885,7 +1952,7 @@
         <v>3</v>
       </c>
       <c r="AV8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
@@ -1894,7 +1961,7 @@
         <v>1</v>
       </c>
       <c r="AY8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AZ8" t="n">
         <v>16</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -1935,43 +2002,43 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E9" t="n">
         <v>50</v>
       </c>
       <c r="F9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G9" t="n">
-        <v>0.704</v>
+        <v>0.714</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
       </c>
       <c r="I9" t="n">
-        <v>36.6</v>
+        <v>36.7</v>
       </c>
       <c r="J9" t="n">
-        <v>79.90000000000001</v>
+        <v>80</v>
       </c>
       <c r="K9" t="n">
         <v>0.459</v>
       </c>
       <c r="L9" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M9" t="n">
         <v>16.3</v>
       </c>
       <c r="N9" t="n">
-        <v>0.377</v>
+        <v>0.375</v>
       </c>
       <c r="O9" t="n">
-        <v>18.5</v>
+        <v>18.6</v>
       </c>
       <c r="P9" t="n">
-        <v>24.1</v>
+        <v>24.3</v>
       </c>
       <c r="Q9" t="n">
         <v>0.764</v>
@@ -1986,13 +2053,13 @@
         <v>41</v>
       </c>
       <c r="U9" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="V9" t="n">
         <v>11.6</v>
       </c>
       <c r="W9" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X9" t="n">
         <v>5.5</v>
@@ -2001,19 +2068,19 @@
         <v>3.8</v>
       </c>
       <c r="Z9" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AB9" t="n">
-        <v>97.90000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC9" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2031,7 +2098,7 @@
         <v>16</v>
       </c>
       <c r="AJ9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK9" t="n">
         <v>13</v>
@@ -2043,25 +2110,25 @@
         <v>21</v>
       </c>
       <c r="AN9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AO9" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AS9" t="n">
         <v>27</v>
       </c>
       <c r="AT9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU9" t="n">
         <v>7</v>
@@ -2079,7 +2146,7 @@
         <v>3</v>
       </c>
       <c r="AZ9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA9" t="n">
         <v>25</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>2.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
@@ -2210,7 +2277,7 @@
         <v>16</v>
       </c>
       <c r="AI10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AJ10" t="n">
         <v>1</v>
@@ -2225,13 +2292,13 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AO10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ10" t="n">
         <v>19</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -2299,16 +2366,16 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E11" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F11" t="n">
         <v>23</v>
       </c>
       <c r="G11" t="n">
-        <v>0.681</v>
+        <v>0.676</v>
       </c>
       <c r="H11" t="n">
         <v>48.1</v>
@@ -2317,10 +2384,10 @@
         <v>36.8</v>
       </c>
       <c r="J11" t="n">
-        <v>81.8</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L11" t="n">
         <v>7.1</v>
@@ -2329,25 +2396,25 @@
         <v>20.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0.339</v>
+        <v>0.341</v>
       </c>
       <c r="O11" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P11" t="n">
-        <v>22.4</v>
+        <v>22.5</v>
       </c>
       <c r="Q11" t="n">
         <v>0.723</v>
       </c>
       <c r="R11" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S11" t="n">
         <v>32.4</v>
       </c>
       <c r="T11" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="U11" t="n">
         <v>21.6</v>
@@ -2356,7 +2423,7 @@
         <v>14</v>
       </c>
       <c r="W11" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="X11" t="n">
         <v>5.2</v>
@@ -2365,43 +2432,43 @@
         <v>4.5</v>
       </c>
       <c r="Z11" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB11" t="n">
         <v>96.90000000000001</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH11" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AJ11" t="n">
         <v>14</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>13</v>
       </c>
       <c r="AK11" t="n">
         <v>17</v>
       </c>
       <c r="AL11" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AM11" t="n">
         <v>6</v>
@@ -2416,19 +2483,19 @@
         <v>26</v>
       </c>
       <c r="AQ11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AS11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AU11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV11" t="n">
         <v>9</v>
@@ -2440,16 +2507,16 @@
         <v>6</v>
       </c>
       <c r="AY11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BA11" t="n">
         <v>27</v>
       </c>
       <c r="BB11" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E12" t="n">
         <v>29</v>
       </c>
       <c r="F12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G12" t="n">
-        <v>0.403</v>
+        <v>0.408</v>
       </c>
       <c r="H12" t="n">
         <v>48.2</v>
@@ -2505,13 +2572,13 @@
         <v>0.443</v>
       </c>
       <c r="L12" t="n">
-        <v>9.1</v>
+        <v>9</v>
       </c>
       <c r="M12" t="n">
-        <v>24.4</v>
+        <v>24.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.371</v>
+        <v>0.369</v>
       </c>
       <c r="O12" t="n">
         <v>18.8</v>
@@ -2520,7 +2587,7 @@
         <v>24.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.769</v>
+        <v>0.767</v>
       </c>
       <c r="R12" t="n">
         <v>11.3</v>
@@ -2529,13 +2596,13 @@
         <v>31.9</v>
       </c>
       <c r="T12" t="n">
-        <v>43.1</v>
+        <v>43.2</v>
       </c>
       <c r="U12" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="V12" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W12" t="n">
         <v>7.7</v>
@@ -2547,19 +2614,19 @@
         <v>5.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="AA12" t="n">
         <v>21.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.8</v>
+        <v>103.6</v>
       </c>
       <c r="AC12" t="n">
         <v>-2.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
         <v>21</v>
@@ -2589,7 +2656,7 @@
         <v>3</v>
       </c>
       <c r="AN12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO12" t="n">
         <v>12</v>
@@ -2598,7 +2665,7 @@
         <v>18</v>
       </c>
       <c r="AQ12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AR12" t="n">
         <v>17</v>
@@ -2613,13 +2680,13 @@
         <v>9</v>
       </c>
       <c r="AV12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AW12" t="n">
         <v>10</v>
       </c>
       <c r="AX12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AY12" t="n">
         <v>22</v>
@@ -2634,7 +2701,7 @@
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -2663,46 +2730,46 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E13" t="n">
         <v>21</v>
       </c>
       <c r="F13" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G13" t="n">
-        <v>0.296</v>
+        <v>0.3</v>
       </c>
       <c r="H13" t="n">
         <v>48.4</v>
       </c>
       <c r="I13" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="J13" t="n">
         <v>78.5</v>
       </c>
       <c r="K13" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="L13" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="M13" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="N13" t="n">
-        <v>0.323</v>
+        <v>0.324</v>
       </c>
       <c r="O13" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="P13" t="n">
-        <v>26.7</v>
+        <v>26.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.784</v>
+        <v>0.783</v>
       </c>
       <c r="R13" t="n">
         <v>9.5</v>
@@ -2714,7 +2781,7 @@
         <v>39.8</v>
       </c>
       <c r="U13" t="n">
-        <v>21</v>
+        <v>21.1</v>
       </c>
       <c r="V13" t="n">
         <v>14.3</v>
@@ -2732,16 +2799,16 @@
         <v>21.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>93.7</v>
+        <v>93.8</v>
       </c>
       <c r="AC13" t="n">
         <v>-6.6</v>
       </c>
       <c r="AD13" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2753,7 +2820,7 @@
         <v>25</v>
       </c>
       <c r="AH13" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI13" t="n">
         <v>30</v>
@@ -2786,13 +2853,13 @@
         <v>27</v>
       </c>
       <c r="AS13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT13" t="n">
         <v>29</v>
       </c>
       <c r="AU13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AV13" t="n">
         <v>11</v>
@@ -2804,7 +2871,7 @@
         <v>16</v>
       </c>
       <c r="AY13" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ13" t="n">
         <v>18</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -2845,40 +2912,40 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E14" t="n">
         <v>49</v>
       </c>
       <c r="F14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G14" t="n">
-        <v>0.681</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H14" t="n">
         <v>48.2</v>
       </c>
       <c r="I14" t="n">
-        <v>39.6</v>
+        <v>39.7</v>
       </c>
       <c r="J14" t="n">
         <v>83.2</v>
       </c>
       <c r="K14" t="n">
-        <v>0.476</v>
+        <v>0.477</v>
       </c>
       <c r="L14" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M14" t="n">
-        <v>20.8</v>
+        <v>20.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0.373</v>
+        <v>0.374</v>
       </c>
       <c r="O14" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="P14" t="n">
         <v>27.9</v>
@@ -2890,10 +2957,10 @@
         <v>10.9</v>
       </c>
       <c r="S14" t="n">
-        <v>33.3</v>
+        <v>33.4</v>
       </c>
       <c r="T14" t="n">
-        <v>44.2</v>
+        <v>44.3</v>
       </c>
       <c r="U14" t="n">
         <v>24</v>
@@ -2917,13 +2984,13 @@
         <v>22.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>108.2</v>
+        <v>108.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AD14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -2947,10 +3014,10 @@
         <v>3</v>
       </c>
       <c r="AL14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AN14" t="n">
         <v>8</v>
@@ -2989,7 +3056,7 @@
         <v>14</v>
       </c>
       <c r="AZ14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -3027,25 +3094,25 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E15" t="n">
         <v>18</v>
       </c>
       <c r="F15" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G15" t="n">
-        <v>0.254</v>
+        <v>0.257</v>
       </c>
       <c r="H15" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I15" t="n">
         <v>37</v>
       </c>
       <c r="J15" t="n">
-        <v>81.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="K15" t="n">
         <v>0.452</v>
@@ -3054,16 +3121,16 @@
         <v>7.6</v>
       </c>
       <c r="M15" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="N15" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O15" t="n">
         <v>18.4</v>
       </c>
       <c r="P15" t="n">
-        <v>25.2</v>
+        <v>25.3</v>
       </c>
       <c r="Q15" t="n">
         <v>0.729</v>
@@ -3072,16 +3139,16 @@
         <v>10.4</v>
       </c>
       <c r="S15" t="n">
-        <v>31.3</v>
+        <v>31.2</v>
       </c>
       <c r="T15" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U15" t="n">
         <v>19.1</v>
       </c>
       <c r="V15" t="n">
-        <v>15.5</v>
+        <v>15.4</v>
       </c>
       <c r="W15" t="n">
         <v>6.2</v>
@@ -3093,19 +3160,19 @@
         <v>5</v>
       </c>
       <c r="Z15" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="AA15" t="n">
         <v>22.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>100</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="AC15" t="n">
         <v>-6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
@@ -3117,13 +3184,13 @@
         <v>28</v>
       </c>
       <c r="AH15" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="AI15" t="n">
         <v>13</v>
       </c>
       <c r="AJ15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AK15" t="n">
         <v>15</v>
@@ -3153,7 +3220,7 @@
         <v>12</v>
       </c>
       <c r="AT15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU15" t="n">
         <v>28</v>
@@ -3162,7 +3229,7 @@
         <v>28</v>
       </c>
       <c r="AW15" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AX15" t="n">
         <v>15</v>
@@ -3171,13 +3238,13 @@
         <v>18</v>
       </c>
       <c r="AZ15" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BA15" t="n">
         <v>6</v>
       </c>
       <c r="BB15" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BC15" t="n">
         <v>24</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E16" t="n">
         <v>13</v>
       </c>
       <c r="F16" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G16" t="n">
-        <v>0.183</v>
+        <v>0.186</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
@@ -3227,28 +3294,28 @@
         <v>35</v>
       </c>
       <c r="J16" t="n">
-        <v>77.8</v>
+        <v>77.7</v>
       </c>
       <c r="K16" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L16" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="M16" t="n">
-        <v>15.6</v>
+        <v>15.4</v>
       </c>
       <c r="N16" t="n">
-        <v>0.352</v>
+        <v>0.348</v>
       </c>
       <c r="O16" t="n">
         <v>17.2</v>
       </c>
       <c r="P16" t="n">
-        <v>23.8</v>
+        <v>23.7</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.722</v>
+        <v>0.723</v>
       </c>
       <c r="R16" t="n">
         <v>9.1</v>
@@ -3257,13 +3324,13 @@
         <v>28.8</v>
       </c>
       <c r="T16" t="n">
-        <v>38</v>
+        <v>37.9</v>
       </c>
       <c r="U16" t="n">
         <v>20.2</v>
       </c>
       <c r="V16" t="n">
-        <v>14.7</v>
+        <v>14.8</v>
       </c>
       <c r="W16" t="n">
         <v>7.1</v>
@@ -3287,7 +3354,7 @@
         <v>-8.199999999999999</v>
       </c>
       <c r="AD16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE16" t="n">
         <v>30</v>
@@ -3299,7 +3366,7 @@
         <v>30</v>
       </c>
       <c r="AH16" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI16" t="n">
         <v>28</v>
@@ -3308,16 +3375,16 @@
         <v>29</v>
       </c>
       <c r="AK16" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AL16" t="n">
         <v>24</v>
       </c>
       <c r="AM16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AN16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO16" t="n">
         <v>25</v>
@@ -3326,7 +3393,7 @@
         <v>22</v>
       </c>
       <c r="AQ16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR16" t="n">
         <v>29</v>
@@ -3338,13 +3405,13 @@
         <v>30</v>
       </c>
       <c r="AU16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX16" t="n">
         <v>23</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E17" t="n">
         <v>24</v>
       </c>
       <c r="F17" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G17" t="n">
-        <v>0.343</v>
+        <v>0.348</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3415,13 +3482,13 @@
         <v>0.447</v>
       </c>
       <c r="L17" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="M17" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="N17" t="n">
-        <v>0.342</v>
+        <v>0.341</v>
       </c>
       <c r="O17" t="n">
         <v>17.6</v>
@@ -3433,10 +3500,10 @@
         <v>0.735</v>
       </c>
       <c r="R17" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="S17" t="n">
-        <v>28.5</v>
+        <v>28.6</v>
       </c>
       <c r="T17" t="n">
         <v>41.2</v>
@@ -3457,31 +3524,31 @@
         <v>5.1</v>
       </c>
       <c r="Z17" t="n">
-        <v>21.5</v>
+        <v>21.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB17" t="n">
         <v>95.90000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>-6.6</v>
+        <v>-6.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE17" t="n">
         <v>24</v>
       </c>
       <c r="AF17" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AG17" t="n">
         <v>24</v>
       </c>
       <c r="AH17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AI17" t="n">
         <v>18</v>
@@ -3523,7 +3590,7 @@
         <v>19</v>
       </c>
       <c r="AV17" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AW17" t="n">
         <v>23</v>
@@ -3541,10 +3608,10 @@
         <v>17</v>
       </c>
       <c r="BB17" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BC17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -3573,16 +3640,16 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E18" t="n">
         <v>18</v>
       </c>
       <c r="F18" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G18" t="n">
-        <v>0.257</v>
+        <v>0.261</v>
       </c>
       <c r="H18" t="n">
         <v>48.1</v>
@@ -3591,37 +3658,37 @@
         <v>37.1</v>
       </c>
       <c r="J18" t="n">
-        <v>82.59999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="K18" t="n">
-        <v>0.448</v>
+        <v>0.449</v>
       </c>
       <c r="L18" t="n">
         <v>5.3</v>
       </c>
       <c r="M18" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="N18" t="n">
-        <v>0.344</v>
+        <v>0.343</v>
       </c>
       <c r="O18" t="n">
         <v>15.3</v>
       </c>
       <c r="P18" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.733</v>
+        <v>0.732</v>
       </c>
       <c r="R18" t="n">
-        <v>11.7</v>
+        <v>11.8</v>
       </c>
       <c r="S18" t="n">
         <v>29.7</v>
       </c>
       <c r="T18" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="U18" t="n">
         <v>19.9</v>
@@ -3639,25 +3706,25 @@
         <v>5.8</v>
       </c>
       <c r="Z18" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="AA18" t="n">
-        <v>17.6</v>
+        <v>17.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>94.7</v>
+        <v>94.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>-6.6</v>
+        <v>-6.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE18" t="n">
         <v>27</v>
       </c>
       <c r="AF18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG18" t="n">
         <v>27</v>
@@ -3672,13 +3739,13 @@
         <v>9</v>
       </c>
       <c r="AK18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL18" t="n">
         <v>25</v>
       </c>
       <c r="AM18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN18" t="n">
         <v>24</v>
@@ -3693,16 +3760,16 @@
         <v>21</v>
       </c>
       <c r="AR18" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AS18" t="n">
         <v>22</v>
       </c>
       <c r="AT18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AU18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV18" t="n">
         <v>23</v>
@@ -3726,7 +3793,7 @@
         <v>28</v>
       </c>
       <c r="BC18" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BD18" t="n">
         <v>10</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -3755,52 +3822,52 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E19" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F19" t="n">
         <v>41</v>
       </c>
       <c r="G19" t="n">
-        <v>0.431</v>
+        <v>0.423</v>
       </c>
       <c r="H19" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I19" t="n">
-        <v>34.6</v>
+        <v>34.5</v>
       </c>
       <c r="J19" t="n">
         <v>78.3</v>
       </c>
       <c r="K19" t="n">
-        <v>0.442</v>
+        <v>0.44</v>
       </c>
       <c r="L19" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="M19" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="N19" t="n">
-        <v>0.349</v>
+        <v>0.346</v>
       </c>
       <c r="O19" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="P19" t="n">
-        <v>27.8</v>
+        <v>27.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.73</v>
+        <v>0.731</v>
       </c>
       <c r="R19" t="n">
         <v>11.4</v>
       </c>
       <c r="S19" t="n">
-        <v>31</v>
+        <v>30.9</v>
       </c>
       <c r="T19" t="n">
         <v>42.3</v>
@@ -3809,7 +3876,7 @@
         <v>23.3</v>
       </c>
       <c r="V19" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W19" t="n">
         <v>6.4</v>
@@ -3824,16 +3891,16 @@
         <v>22.8</v>
       </c>
       <c r="AA19" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>95.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="AC19" t="n">
-        <v>-4.7</v>
+        <v>-4.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE19" t="n">
         <v>19</v>
@@ -3845,7 +3912,7 @@
         <v>20</v>
       </c>
       <c r="AH19" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AI19" t="n">
         <v>29</v>
@@ -3860,10 +3927,10 @@
         <v>20</v>
       </c>
       <c r="AM19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO19" t="n">
         <v>10</v>
@@ -3881,7 +3948,7 @@
         <v>13</v>
       </c>
       <c r="AT19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU19" t="n">
         <v>6</v>
@@ -3890,13 +3957,13 @@
         <v>26</v>
       </c>
       <c r="AW19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX19" t="n">
         <v>17</v>
       </c>
       <c r="AY19" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AZ19" t="n">
         <v>26</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -3937,61 +4004,61 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E20" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F20" t="n">
         <v>21</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7</v>
+        <v>0.696</v>
       </c>
       <c r="H20" t="n">
         <v>48.4</v>
       </c>
       <c r="I20" t="n">
-        <v>38.4</v>
+        <v>38.5</v>
       </c>
       <c r="J20" t="n">
-        <v>82.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="K20" t="n">
-        <v>0.463</v>
+        <v>0.464</v>
       </c>
       <c r="L20" t="n">
-        <v>7.8</v>
+        <v>7.7</v>
       </c>
       <c r="M20" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="N20" t="n">
-        <v>0.391</v>
+        <v>0.39</v>
       </c>
       <c r="O20" t="n">
-        <v>15.9</v>
+        <v>15.8</v>
       </c>
       <c r="P20" t="n">
         <v>20.5</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.773</v>
+        <v>0.771</v>
       </c>
       <c r="R20" t="n">
         <v>11.6</v>
       </c>
       <c r="S20" t="n">
-        <v>30.6</v>
+        <v>30.7</v>
       </c>
       <c r="T20" t="n">
-        <v>42.2</v>
+        <v>42.3</v>
       </c>
       <c r="U20" t="n">
         <v>21.6</v>
       </c>
       <c r="V20" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="W20" t="n">
         <v>7.7</v>
@@ -4006,46 +4073,46 @@
         <v>18.8</v>
       </c>
       <c r="AA20" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="AB20" t="n">
         <v>100.5</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AE20" t="n">
+        <v>4</v>
+      </c>
+      <c r="AF20" t="n">
         <v>3</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2</v>
       </c>
       <c r="AG20" t="n">
         <v>3</v>
       </c>
       <c r="AH20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI20" t="n">
         <v>6</v>
       </c>
       <c r="AJ20" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AK20" t="n">
         <v>8</v>
       </c>
       <c r="AL20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM20" t="n">
         <v>9</v>
       </c>
       <c r="AN20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO20" t="n">
         <v>29</v>
@@ -4066,13 +4133,13 @@
         <v>12</v>
       </c>
       <c r="AU20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV20" t="n">
         <v>3</v>
       </c>
       <c r="AW20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX20" t="n">
         <v>28</v>
@@ -4087,7 +4154,7 @@
         <v>28</v>
       </c>
       <c r="BB20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC20" t="n">
         <v>5</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -4119,28 +4186,28 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F21" t="n">
         <v>51</v>
       </c>
       <c r="G21" t="n">
-        <v>0.282</v>
+        <v>0.271</v>
       </c>
       <c r="H21" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>35.5</v>
+        <v>35.4</v>
       </c>
       <c r="J21" t="n">
-        <v>81.2</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.437</v>
+        <v>0.438</v>
       </c>
       <c r="L21" t="n">
         <v>5.8</v>
@@ -4155,19 +4222,19 @@
         <v>18.7</v>
       </c>
       <c r="P21" t="n">
-        <v>25.9</v>
+        <v>25.8</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.723</v>
+        <v>0.725</v>
       </c>
       <c r="R21" t="n">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="S21" t="n">
-        <v>29.7</v>
+        <v>29.5</v>
       </c>
       <c r="T21" t="n">
-        <v>42</v>
+        <v>41.7</v>
       </c>
       <c r="U21" t="n">
         <v>18.3</v>
@@ -4176,7 +4243,7 @@
         <v>14.6</v>
       </c>
       <c r="W21" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X21" t="n">
         <v>2.6</v>
@@ -4188,16 +4255,16 @@
         <v>21.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AB21" t="n">
-        <v>95.5</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC21" t="n">
-        <v>-6.9</v>
+        <v>-7.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE21" t="n">
         <v>26</v>
@@ -4209,7 +4276,7 @@
         <v>26</v>
       </c>
       <c r="AH21" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI21" t="n">
         <v>27</v>
@@ -4230,7 +4297,7 @@
         <v>28</v>
       </c>
       <c r="AO21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP21" t="n">
         <v>11</v>
@@ -4239,13 +4306,13 @@
         <v>25</v>
       </c>
       <c r="AR21" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AS21" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AT21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AU21" t="n">
         <v>30</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4464,7 @@
         <v>11</v>
       </c>
       <c r="AJ22" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AK22" t="n">
         <v>5</v>
@@ -4436,16 +4503,16 @@
         <v>13</v>
       </c>
       <c r="AW22" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AX22" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AY22" t="n">
         <v>7</v>
       </c>
       <c r="AZ22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA22" t="n">
         <v>3</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -4483,43 +4550,43 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E23" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F23" t="n">
         <v>35</v>
       </c>
       <c r="G23" t="n">
-        <v>0.514</v>
+        <v>0.507</v>
       </c>
       <c r="H23" t="n">
         <v>48.2</v>
       </c>
       <c r="I23" t="n">
-        <v>37.3</v>
+        <v>37.2</v>
       </c>
       <c r="J23" t="n">
         <v>80.90000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>0.461</v>
+        <v>0.46</v>
       </c>
       <c r="L23" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="M23" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="N23" t="n">
-        <v>0.32</v>
+        <v>0.316</v>
       </c>
       <c r="O23" t="n">
         <v>18.6</v>
       </c>
       <c r="P23" t="n">
-        <v>26.4</v>
+        <v>26.3</v>
       </c>
       <c r="Q23" t="n">
         <v>0.705</v>
@@ -4528,25 +4595,25 @@
         <v>13.2</v>
       </c>
       <c r="S23" t="n">
-        <v>29</v>
+        <v>28.9</v>
       </c>
       <c r="T23" t="n">
         <v>42.1</v>
       </c>
       <c r="U23" t="n">
-        <v>20.3</v>
+        <v>20</v>
       </c>
       <c r="V23" t="n">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="W23" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="X23" t="n">
         <v>4.9</v>
       </c>
       <c r="Y23" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z23" t="n">
         <v>19.8</v>
@@ -4555,13 +4622,13 @@
         <v>21.1</v>
       </c>
       <c r="AB23" t="n">
-        <v>96.8</v>
+        <v>96.5</v>
       </c>
       <c r="AC23" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE23" t="n">
         <v>15</v>
@@ -4582,7 +4649,7 @@
         <v>17</v>
       </c>
       <c r="AK23" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL23" t="n">
         <v>30</v>
@@ -4594,7 +4661,7 @@
         <v>30</v>
       </c>
       <c r="AO23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP23" t="n">
         <v>10</v>
@@ -4603,7 +4670,7 @@
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AS23" t="n">
         <v>28</v>
@@ -4612,7 +4679,7 @@
         <v>13</v>
       </c>
       <c r="AU23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AV23" t="n">
         <v>18</v>
@@ -4633,7 +4700,7 @@
         <v>15</v>
       </c>
       <c r="BB23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC23" t="n">
         <v>14</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -4665,25 +4732,25 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E24" t="n">
         <v>47</v>
       </c>
       <c r="F24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G24" t="n">
-        <v>0.662</v>
+        <v>0.671</v>
       </c>
       <c r="H24" t="n">
         <v>48.3</v>
       </c>
       <c r="I24" t="n">
-        <v>41.4</v>
+        <v>41.5</v>
       </c>
       <c r="J24" t="n">
-        <v>82.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K24" t="n">
         <v>0.499</v>
@@ -4692,7 +4759,7 @@
         <v>8.6</v>
       </c>
       <c r="M24" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="N24" t="n">
         <v>0.391</v>
@@ -4701,25 +4768,25 @@
         <v>18.6</v>
       </c>
       <c r="P24" t="n">
-        <v>23.6</v>
+        <v>23.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.786</v>
+        <v>0.785</v>
       </c>
       <c r="R24" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="S24" t="n">
-        <v>32.4</v>
+        <v>32.5</v>
       </c>
       <c r="T24" t="n">
-        <v>41</v>
+        <v>41.2</v>
       </c>
       <c r="U24" t="n">
         <v>26.7</v>
       </c>
       <c r="V24" t="n">
-        <v>14.5</v>
+        <v>14.4</v>
       </c>
       <c r="W24" t="n">
         <v>6.6</v>
@@ -4737,31 +4804,31 @@
         <v>20.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>110</v>
+        <v>110.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
       <c r="AD24" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE24" t="n">
         <v>7</v>
       </c>
       <c r="AF24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AG24" t="n">
         <v>7</v>
       </c>
       <c r="AH24" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AJ24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK24" t="n">
         <v>1</v>
@@ -4773,10 +4840,10 @@
         <v>4</v>
       </c>
       <c r="AN24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP24" t="n">
         <v>23</v>
@@ -4788,10 +4855,10 @@
         <v>30</v>
       </c>
       <c r="AS24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AT24" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
@@ -4818,7 +4885,7 @@
         <v>2</v>
       </c>
       <c r="BC24" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -4946,7 +5013,7 @@
         <v>23</v>
       </c>
       <c r="AK25" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AL25" t="n">
         <v>15</v>
@@ -4955,7 +5022,7 @@
         <v>17</v>
       </c>
       <c r="AN25" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO25" t="n">
         <v>23</v>
@@ -4964,7 +5031,7 @@
         <v>25</v>
       </c>
       <c r="AQ25" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AR25" t="n">
         <v>21</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -5029,16 +5096,16 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E26" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="F26" t="n">
         <v>39</v>
       </c>
       <c r="G26" t="n">
-        <v>0.451</v>
+        <v>0.443</v>
       </c>
       <c r="H26" t="n">
         <v>48.4</v>
@@ -5047,28 +5114,28 @@
         <v>36.8</v>
       </c>
       <c r="J26" t="n">
-        <v>80</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.46</v>
+        <v>0.461</v>
       </c>
       <c r="L26" t="n">
         <v>6.3</v>
       </c>
       <c r="M26" t="n">
-        <v>17</v>
+        <v>16.8</v>
       </c>
       <c r="N26" t="n">
-        <v>0.37</v>
+        <v>0.374</v>
       </c>
       <c r="O26" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="P26" t="n">
         <v>27.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.796</v>
+        <v>0.793</v>
       </c>
       <c r="R26" t="n">
         <v>10.4</v>
@@ -5077,10 +5144,10 @@
         <v>30</v>
       </c>
       <c r="T26" t="n">
-        <v>40.4</v>
+        <v>40.3</v>
       </c>
       <c r="U26" t="n">
-        <v>19.1</v>
+        <v>19</v>
       </c>
       <c r="V26" t="n">
         <v>15.9</v>
@@ -5098,16 +5165,16 @@
         <v>22.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>101.9</v>
+        <v>101.8</v>
       </c>
       <c r="AC26" t="n">
-        <v>-2.4</v>
+        <v>-2.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE26" t="n">
         <v>18</v>
@@ -5119,28 +5186,28 @@
         <v>18</v>
       </c>
       <c r="AH26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AI26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK26" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL26" t="n">
         <v>17</v>
       </c>
       <c r="AM26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AN26" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="AO26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AP26" t="n">
         <v>6</v>
@@ -5152,7 +5219,7 @@
         <v>23</v>
       </c>
       <c r="AS26" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT26" t="n">
         <v>27</v>
@@ -5164,7 +5231,7 @@
         <v>29</v>
       </c>
       <c r="AW26" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AX26" t="n">
         <v>24</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -5211,25 +5278,25 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E27" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F27" t="n">
         <v>23</v>
       </c>
       <c r="G27" t="n">
-        <v>0.681</v>
+        <v>0.676</v>
       </c>
       <c r="H27" t="n">
         <v>48.1</v>
       </c>
       <c r="I27" t="n">
-        <v>35.7</v>
+        <v>35.6</v>
       </c>
       <c r="J27" t="n">
-        <v>78.5</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K27" t="n">
         <v>0.454</v>
@@ -5241,31 +5308,31 @@
         <v>20.2</v>
       </c>
       <c r="N27" t="n">
-        <v>0.371</v>
+        <v>0.372</v>
       </c>
       <c r="O27" t="n">
         <v>16.9</v>
       </c>
       <c r="P27" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.764</v>
+        <v>0.765</v>
       </c>
       <c r="R27" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S27" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="T27" t="n">
         <v>41.2</v>
       </c>
       <c r="U27" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="V27" t="n">
-        <v>12.6</v>
+        <v>12.7</v>
       </c>
       <c r="W27" t="n">
         <v>6.5</v>
@@ -5286,28 +5353,28 @@
         <v>95.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AD27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AH27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AI27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AJ27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AK27" t="n">
         <v>14</v>
@@ -5319,7 +5386,7 @@
         <v>8</v>
       </c>
       <c r="AN27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO27" t="n">
         <v>26</v>
@@ -5328,7 +5395,7 @@
         <v>27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR27" t="n">
         <v>25</v>
@@ -5349,7 +5416,7 @@
         <v>22</v>
       </c>
       <c r="AX27" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AY27" t="n">
         <v>11</v>
@@ -5358,13 +5425,13 @@
         <v>2</v>
       </c>
       <c r="BA27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB27" t="n">
         <v>24</v>
       </c>
       <c r="BC27" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BD27" t="n">
         <v>10</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E28" t="n">
         <v>17</v>
       </c>
       <c r="F28" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G28" t="n">
-        <v>0.236</v>
+        <v>0.239</v>
       </c>
       <c r="H28" t="n">
         <v>48.3</v>
@@ -5423,7 +5490,7 @@
         <v>11.8</v>
       </c>
       <c r="N28" t="n">
-        <v>0.338</v>
+        <v>0.341</v>
       </c>
       <c r="O28" t="n">
         <v>17.7</v>
@@ -5432,34 +5499,34 @@
         <v>23</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.768</v>
+        <v>0.767</v>
       </c>
       <c r="R28" t="n">
-        <v>11.9</v>
+        <v>11.8</v>
       </c>
       <c r="S28" t="n">
         <v>32.7</v>
       </c>
       <c r="T28" t="n">
-        <v>44.6</v>
+        <v>44.5</v>
       </c>
       <c r="U28" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V28" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="W28" t="n">
         <v>6.4</v>
       </c>
       <c r="X28" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y28" t="n">
         <v>5.4</v>
       </c>
       <c r="Z28" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="AA28" t="n">
         <v>19.8</v>
@@ -5471,7 +5538,7 @@
         <v>-8.699999999999999</v>
       </c>
       <c r="AD28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AE28" t="n">
         <v>29</v>
@@ -5492,7 +5559,7 @@
         <v>4</v>
       </c>
       <c r="AK28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL28" t="n">
         <v>29</v>
@@ -5519,7 +5586,7 @@
         <v>2</v>
       </c>
       <c r="AT28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU28" t="n">
         <v>15</v>
@@ -5537,7 +5604,7 @@
         <v>26</v>
       </c>
       <c r="AZ28" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BA28" t="n">
         <v>26</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -5575,16 +5642,16 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E29" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F29" t="n">
         <v>35</v>
       </c>
       <c r="G29" t="n">
-        <v>0.507</v>
+        <v>0.5</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
@@ -5593,67 +5660,67 @@
         <v>38.2</v>
       </c>
       <c r="J29" t="n">
-        <v>81.90000000000001</v>
+        <v>82</v>
       </c>
       <c r="K29" t="n">
-        <v>0.467</v>
+        <v>0.466</v>
       </c>
       <c r="L29" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M29" t="n">
-        <v>18</v>
+        <v>18.1</v>
       </c>
       <c r="N29" t="n">
         <v>0.402</v>
       </c>
       <c r="O29" t="n">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P29" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.8120000000000001</v>
       </c>
       <c r="R29" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S29" t="n">
         <v>30.5</v>
       </c>
       <c r="T29" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="U29" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="V29" t="n">
         <v>11.8</v>
       </c>
       <c r="W29" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X29" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="Y29" t="n">
         <v>4.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="AA29" t="n">
         <v>18.3</v>
       </c>
       <c r="AB29" t="n">
-        <v>99.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="AC29" t="n">
         <v>2.9</v>
       </c>
       <c r="AD29" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE29" t="n">
         <v>17</v>
@@ -5665,7 +5732,7 @@
         <v>17</v>
       </c>
       <c r="AH29" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AI29" t="n">
         <v>7</v>
@@ -5719,13 +5786,13 @@
         <v>5</v>
       </c>
       <c r="AZ29" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BA29" t="n">
         <v>29</v>
       </c>
       <c r="BB29" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BC29" t="n">
         <v>12</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -5865,10 +5932,10 @@
         <v>27</v>
       </c>
       <c r="AN30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AP30" t="n">
         <v>2</v>
@@ -5889,7 +5956,7 @@
         <v>2</v>
       </c>
       <c r="AV30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW30" t="n">
         <v>3</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
@@ -5939,16 +6006,16 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E31" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F31" t="n">
         <v>34</v>
       </c>
       <c r="G31" t="n">
-        <v>0.521</v>
+        <v>0.514</v>
       </c>
       <c r="H31" t="n">
         <v>48.6</v>
@@ -5966,7 +6033,7 @@
         <v>6.7</v>
       </c>
       <c r="M31" t="n">
-        <v>19.4</v>
+        <v>19.3</v>
       </c>
       <c r="N31" t="n">
         <v>0.346</v>
@@ -5975,25 +6042,25 @@
         <v>19.1</v>
       </c>
       <c r="P31" t="n">
-        <v>24.2</v>
+        <v>24.3</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.787</v>
+        <v>0.786</v>
       </c>
       <c r="R31" t="n">
         <v>12.2</v>
       </c>
       <c r="S31" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="T31" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="U31" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="V31" t="n">
-        <v>13.2</v>
+        <v>13.3</v>
       </c>
       <c r="W31" t="n">
         <v>7.8</v>
@@ -6002,7 +6069,7 @@
         <v>4.9</v>
       </c>
       <c r="Y31" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z31" t="n">
         <v>19.7</v>
@@ -6011,13 +6078,13 @@
         <v>20.3</v>
       </c>
       <c r="AB31" t="n">
-        <v>98.2</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AE31" t="n">
         <v>15</v>
@@ -6035,7 +6102,7 @@
         <v>21</v>
       </c>
       <c r="AJ31" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AK31" t="n">
         <v>24</v>
@@ -6044,28 +6111,28 @@
         <v>14</v>
       </c>
       <c r="AM31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AN31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO31" t="n">
         <v>11</v>
       </c>
       <c r="AP31" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ31" t="n">
         <v>4</v>
       </c>
       <c r="AR31" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AS31" t="n">
         <v>25</v>
       </c>
       <c r="AT31" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AU31" t="n">
         <v>27</v>
@@ -6080,13 +6147,13 @@
         <v>13</v>
       </c>
       <c r="AY31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ31" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB31" t="n">
         <v>14</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>3-26-2007-08</t>
+          <t>2008-03-26</t>
         </is>
       </c>
     </row>
